--- a/doctool/test/auto/scenario27/システム機能設計書_サンプル_S27_expected.xlsx
+++ b/doctool/test/auto/scenario27/システム機能設計書_サンプル_S27_expected.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PJ\01.Nablarch\repo\review-support-tool\doctool\test\temp_dir\scenario15\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PJ\01.Nablarch\repo\review-support-tool\doctool\test\temp_dir\scenario27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01A1C329-FFB0-4A1A-90E4-D6C4E8001D4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{880E4AB2-699E-4BD0-864A-3F6DCF9E9095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1330,7 +1330,7 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>システム機能設計書_サンプル_S15</t>
+    <t>システム機能設計書_サンプル_S27</t>
   </si>
   <si>
     <t>B5</t>
@@ -3392,7 +3392,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0538285-4E32-426B-BD85-0DFDD90BC7E8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553EC503-E974-4EA2-A92E-CBD71001D5DF}">
   <sheetPr codeName="ErrorSheetTemplate">
     <tabColor theme="3" tint="0.59999389629810485"/>
   </sheetPr>
@@ -3452,10 +3452,10 @@
   </sheetData>
   <phoneticPr fontId="10"/>
   <hyperlinks>
-    <hyperlink ref="B3" location="'2. WA1020101(プロジェクト登録画面)'!$E$68" display="'2. WA1020101(プロジェクト登録画面)'!$E$68" xr:uid="{74692CB8-035E-42DD-9C57-6A9AA12E4DF7}"/>
-    <hyperlink ref="B4" location="'2. WA1020101(プロジェクト登録画面)'!$E$69" display="'2. WA1020101(プロジェクト登録画面)'!$E$69" xr:uid="{CA9809D3-E479-4E09-BEF0-4B11BACDE3FD}"/>
-    <hyperlink ref="B5" location="'2. WA1020101(プロジェクト登録画面)'!$E$70" display="'2. WA1020101(プロジェクト登録画面)'!$E$70" xr:uid="{94060CBD-89A8-422C-994C-EF150894B934}"/>
-    <hyperlink ref="B6" location="'2. WA1020101(プロジェクト登録画面)'!$E$71" display="'2. WA1020101(プロジェクト登録画面)'!$E$71" xr:uid="{C2FD615F-FBEA-4ED2-8012-8A1CF01B7B95}"/>
+    <hyperlink ref="B3" location="'2. WA1020101(プロジェクト登録画面)'!$E$68" display="'2. WA1020101(プロジェクト登録画面)'!$E$68" xr:uid="{0A72B30D-89D9-4207-B526-0CDFEB69DDB8}"/>
+    <hyperlink ref="B4" location="'2. WA1020101(プロジェクト登録画面)'!$E$69" display="'2. WA1020101(プロジェクト登録画面)'!$E$69" xr:uid="{1CB6BA65-3D80-4B62-86E4-EEBCB2740A51}"/>
+    <hyperlink ref="B5" location="'2. WA1020101(プロジェクト登録画面)'!$E$70" display="'2. WA1020101(プロジェクト登録画面)'!$E$70" xr:uid="{C0F9D4FD-D03B-488A-BE76-49CE0433822A}"/>
+    <hyperlink ref="B6" location="'2. WA1020101(プロジェクト登録画面)'!$E$71" display="'2. WA1020101(プロジェクト登録画面)'!$E$71" xr:uid="{8FA7F807-C8ED-4C8B-9A91-2BB776046753}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3602,7 +3602,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92A909A5-97B6-495F-9A0C-B4E2A4176C9A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9C264EB-0D84-4CFD-8555-A32FF9DB5129}">
   <sheetPr codeName="SheetTemplate">
     <tabColor indexed="44"/>
     <pageSetUpPr fitToPage="1"/>
@@ -4553,19 +4553,19 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K15:K23" xr:uid="{742479BF-A721-40D3-90DB-45C757303FF1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K15:K23" xr:uid="{DADE2831-03EF-4F2D-9003-C369729E8317}">
       <formula1>"未,済"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="B15" location="'2. WA1020101(プロジェクト登録画面)'!$B$5" display="'2. WA1020101(プロジェクト登録画面)'!$B$5" xr:uid="{DDE39580-271C-4A07-861B-C36A48F5A1FD}"/>
-    <hyperlink ref="B16" location="'2. WA1020101(プロジェクト登録画面)'!$E$60" display="'2. WA1020101(プロジェクト登録画面)'!$E$60" xr:uid="{1A0DD86C-AE30-45C9-9E8F-974A6699742F}"/>
-    <hyperlink ref="B17" location="'2. WA1020101(プロジェクト登録画面)'!$E$62" display="'2. WA1020101(プロジェクト登録画面)'!$E$62" xr:uid="{C0518A99-AE36-4EBF-B699-2B407C028E22}"/>
-    <hyperlink ref="B18" location="'2. WA1020101(プロジェクト登録画面)'!$E$63" display="'2. WA1020101(プロジェクト登録画面)'!$E$63" xr:uid="{F4193A14-06DA-497F-A509-8F95730C4CD4}"/>
-    <hyperlink ref="B19" location="'2. WA1020101(プロジェクト登録画面)'!$E$64" display="'2. WA1020101(プロジェクト登録画面)'!$E$64" xr:uid="{BC291CC2-EEA0-4BE4-A633-C67F31E25EF5}"/>
-    <hyperlink ref="B20" location="'2. WA1020101(プロジェクト登録画面)'!$E$65" display="'2. WA1020101(プロジェクト登録画面)'!$E$65" xr:uid="{228B2C98-64DA-482C-83AA-4401B63EC4C5}"/>
-    <hyperlink ref="B21" location="'2. WA1020101(プロジェクト登録画面)'!$E$66" display="'2. WA1020101(プロジェクト登録画面)'!$E$66" xr:uid="{71A3C492-78A0-46BF-BD04-5B2233FEC1E3}"/>
-    <hyperlink ref="B22" location="'2. WA1020101(プロジェクト登録画面)'!$E$67" display="'2. WA1020101(プロジェクト登録画面)'!$E$67" xr:uid="{65833FAB-4701-42D2-9D41-F2C880718CF3}"/>
+    <hyperlink ref="B15" location="'2. WA1020101(プロジェクト登録画面)'!$B$5" display="'2. WA1020101(プロジェクト登録画面)'!$B$5" xr:uid="{8571D6C5-1299-4C7C-B9AF-671C75EE0CC2}"/>
+    <hyperlink ref="B16" location="'2. WA1020101(プロジェクト登録画面)'!$E$60" display="'2. WA1020101(プロジェクト登録画面)'!$E$60" xr:uid="{FBBDEE91-024C-4BE1-A8F8-8CBB7F22E126}"/>
+    <hyperlink ref="B17" location="'2. WA1020101(プロジェクト登録画面)'!$E$62" display="'2. WA1020101(プロジェクト登録画面)'!$E$62" xr:uid="{DAEE31CA-8FB6-4CC5-A807-D43D65237713}"/>
+    <hyperlink ref="B18" location="'2. WA1020101(プロジェクト登録画面)'!$E$63" display="'2. WA1020101(プロジェクト登録画面)'!$E$63" xr:uid="{9E125C1B-F9F2-4361-BD92-DBDC4EDC0342}"/>
+    <hyperlink ref="B19" location="'2. WA1020101(プロジェクト登録画面)'!$E$64" display="'2. WA1020101(プロジェクト登録画面)'!$E$64" xr:uid="{20E27398-459B-4753-80A9-9803454E57C3}"/>
+    <hyperlink ref="B20" location="'2. WA1020101(プロジェクト登録画面)'!$E$65" display="'2. WA1020101(プロジェクト登録画面)'!$E$65" xr:uid="{120A5A9F-929D-4219-B72D-808D3E90040E}"/>
+    <hyperlink ref="B21" location="'2. WA1020101(プロジェクト登録画面)'!$E$66" display="'2. WA1020101(プロジェクト登録画面)'!$E$66" xr:uid="{C9BB56BC-279A-4A99-8F42-28D332D7C62C}"/>
+    <hyperlink ref="B22" location="'2. WA1020101(プロジェクト登録画面)'!$E$67" display="'2. WA1020101(プロジェクト登録画面)'!$E$67" xr:uid="{1C1D0796-5A4C-425D-8863-6DDD93E1B09F}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
   <pageSetup paperSize="9" scale="86" orientation="landscape" verticalDpi="200" r:id="rId1"/>

--- a/doctool/test/auto/scenario27/システム機能設計書_サンプル_S27_expected.xlsx
+++ b/doctool/test/auto/scenario27/システム機能設計書_サンプル_S27_expected.xlsx
@@ -5,40 +5,39 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PJ\01.Nablarch\repo\review-support-tool\doctool\test\temp_dir\scenario27\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PJ\01.Nablarch\repo\review-support-tool\doctool\test\temp_dir\scenario26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{880E4AB2-699E-4BD0-864A-3F6DCF9E9095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4663F348-E824-49E9-B1E2-2B511BA4949C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="エラーシート" sheetId="13" r:id="rId1"/>
-    <sheet name="レビュー結果1回目" sheetId="12" r:id="rId2"/>
-    <sheet name="表紙" sheetId="1" r:id="rId3"/>
-    <sheet name="変更履歴" sheetId="2" r:id="rId4"/>
-    <sheet name="目次" sheetId="3" r:id="rId5"/>
-    <sheet name="1.  画面取引定義" sheetId="4" r:id="rId6"/>
-    <sheet name="2. WA1020101(プロジェクト登録画面)" sheetId="5" r:id="rId7"/>
-    <sheet name="3. WA1020102(プロジェクト登録確認画面)" sheetId="6" r:id="rId8"/>
-    <sheet name="4. WA1020103(プロジェクト登録完了画面)" sheetId="7" r:id="rId9"/>
-    <sheet name="データ" sheetId="8" state="hidden" r:id="rId10"/>
+    <sheet name="レビュー結果1回目" sheetId="11" r:id="rId1"/>
+    <sheet name="表紙" sheetId="1" r:id="rId2"/>
+    <sheet name="変更履歴" sheetId="2" r:id="rId3"/>
+    <sheet name="目次" sheetId="3" r:id="rId4"/>
+    <sheet name="1.  画面取引定義" sheetId="4" r:id="rId5"/>
+    <sheet name="2. WA1020101(プロジェクト登録画面)" sheetId="5" r:id="rId6"/>
+    <sheet name="3. WA1020102(プロジェクト登録確認画面)" sheetId="6" r:id="rId7"/>
+    <sheet name="4. WA1020103(プロジェクト登録完了画面)" sheetId="7" r:id="rId8"/>
+    <sheet name="データ" sheetId="8" state="hidden" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_Toc46209822" localSheetId="5">'1.  画面取引定義'!$B$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'1.  画面取引定義'!$A$1:$AI$21</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'2. WA1020101(プロジェクト登録画面)'!$A$1:$AI$180</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'3. WA1020102(プロジェクト登録確認画面)'!$A$1:$AI$136</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'4. WA1020103(プロジェクト登録完了画面)'!$A$1:$AI$68</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">データ!$A$1:$E$15</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">レビュー結果1回目!$A$1:$K$23</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">表紙!$A$1:$S$39</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">変更履歴!$A$1:$AI$34</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">目次!$A$1:$AI$33</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'1.  画面取引定義'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'2. WA1020101(プロジェクト登録画面)'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="7">'3. WA1020102(プロジェクト登録確認画面)'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="8">'4. WA1020103(プロジェクト登録完了画面)'!$1:$4</definedName>
+    <definedName name="_Toc46209822" localSheetId="4">'1.  画面取引定義'!$B$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'1.  画面取引定義'!$A$1:$AI$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'2. WA1020101(プロジェクト登録画面)'!$A$1:$AI$180</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'3. WA1020102(プロジェクト登録確認画面)'!$A$1:$AI$136</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'4. WA1020103(プロジェクト登録完了画面)'!$A$1:$AI$68</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">データ!$A$1:$E$15</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">レビュー結果1回目!$A$1:$N$27</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">表紙!$A$1:$S$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">変更履歴!$A$1:$AI$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">目次!$A$1:$AI$33</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'1.  画面取引定義'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'2. WA1020101(プロジェクト登録画面)'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'3. WA1020102(プロジェクト登録確認画面)'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'4. WA1020103(プロジェクト登録完了画面)'!$1:$4</definedName>
     <definedName name="引継項目格納先">データ!$B$2:$B$2</definedName>
     <definedName name="画面項目種類">データ!$A$2:$A$14</definedName>
     <definedName name="種別一覧">データ!$C$2:$C$7</definedName>
@@ -279,7 +278,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="907" uniqueCount="352">
   <si>
     <t>第１．２版</t>
   </si>
@@ -1330,7 +1329,7 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>システム機能設計書_サンプル_S27</t>
+    <t>システム機能設計書_サンプル_S26</t>
   </si>
   <si>
     <t>B5</t>
@@ -1404,41 +1403,6 @@
     <t>記述誤りの指摘例（カテゴリf）。</t>
   </si>
   <si>
-    <t>＜エラー＞</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>エラー内容</t>
-    <rPh sb="3" eb="5">
-      <t>ナイヨウ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>未登録の指摘分類エイリアスが記入されています: i</t>
-  </si>
-  <si>
-    <t>2. WA1020101(プロジェクト登録画面)'!$E$68</t>
-  </si>
-  <si>
-    <t>未登録の指摘分類エイリアスが記入されています: j</t>
-  </si>
-  <si>
-    <t>2. WA1020101(プロジェクト登録画面)'!$E$69</t>
-  </si>
-  <si>
-    <t>未登録の指摘分類エイリアスが記入されています: k</t>
-  </si>
-  <si>
-    <t>2. WA1020101(プロジェクト登録画面)'!$E$70</t>
-  </si>
-  <si>
-    <t>未登録の指摘分類エイリアスが記入されています: l</t>
-  </si>
-  <si>
-    <t>2. WA1020101(プロジェクト登録画面)'!$E$71</t>
-  </si>
-  <si>
     <t>g</t>
     <phoneticPr fontId="13"/>
   </si>
@@ -1447,6 +1411,22 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
+    <t>i</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>j</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>k</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>l</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
     <t>91_疑問点、確認</t>
     <phoneticPr fontId="13"/>
   </si>
@@ -1455,6 +1435,22 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
+    <t>93_仕様変更</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>94_テスト項目漏れ</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>95_テスト漏れ</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>96_その他</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
     <t>E66</t>
   </si>
   <si>
@@ -1471,6 +1467,42 @@
   </si>
   <si>
     <t>改善要望の指摘例（カテゴリh）。</t>
+  </si>
+  <si>
+    <t>E68</t>
+  </si>
+  <si>
+    <t>i</t>
+  </si>
+  <si>
+    <t>仕様変更の指摘例（カテゴリi）。</t>
+  </si>
+  <si>
+    <t>E69</t>
+  </si>
+  <si>
+    <t>j</t>
+  </si>
+  <si>
+    <t>テスト項目漏れの指摘例（カテゴリj）。</t>
+  </si>
+  <si>
+    <t>E70</t>
+  </si>
+  <si>
+    <t>k</t>
+  </si>
+  <si>
+    <t>テスト漏れの指摘例（カテゴリk）。</t>
+  </si>
+  <si>
+    <t>E71</t>
+  </si>
+  <si>
+    <t>l</t>
+  </si>
+  <si>
+    <t>その他の指摘例（カテゴリl）。</t>
   </si>
 </sst>
 </file>
@@ -2192,7 +2224,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="300">
+  <cellXfs count="299">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2952,10 +2984,6 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="11" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="5" quotePrefix="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="12">
@@ -3392,243 +3420,31 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553EC503-E974-4EA2-A92E-CBD71001D5DF}">
-  <sheetPr codeName="ErrorSheetTemplate">
-    <tabColor theme="3" tint="0.59999389629810485"/>
-  </sheetPr>
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <cols>
-    <col min="1" max="1" width="105.1640625" style="287" customWidth="1"/>
-    <col min="2" max="2" width="42.1640625" style="262" customWidth="1"/>
-    <col min="3" max="16384" width="9.33203125" style="262"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A1" s="286" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A2" s="287" t="s">
-        <v>323</v>
-      </c>
-      <c r="B2" s="262" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A3" s="287" t="s">
-        <v>324</v>
-      </c>
-      <c r="B3" s="299" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A4" s="287" t="s">
-        <v>326</v>
-      </c>
-      <c r="B4" s="299" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A5" s="287" t="s">
-        <v>328</v>
-      </c>
-      <c r="B5" s="299" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A6" s="287" t="s">
-        <v>330</v>
-      </c>
-      <c r="B6" s="299" t="s">
-        <v>331</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="10"/>
-  <hyperlinks>
-    <hyperlink ref="B3" location="'2. WA1020101(プロジェクト登録画面)'!$E$68" display="'2. WA1020101(プロジェクト登録画面)'!$E$68" xr:uid="{0A72B30D-89D9-4207-B526-0CDFEB69DDB8}"/>
-    <hyperlink ref="B4" location="'2. WA1020101(プロジェクト登録画面)'!$E$69" display="'2. WA1020101(プロジェクト登録画面)'!$E$69" xr:uid="{1CB6BA65-3D80-4B62-86E4-EEBCB2740A51}"/>
-    <hyperlink ref="B5" location="'2. WA1020101(プロジェクト登録画面)'!$E$70" display="'2. WA1020101(プロジェクト登録画面)'!$E$70" xr:uid="{C0F9D4FD-D03B-488A-BE76-49CE0433822A}"/>
-    <hyperlink ref="B6" location="'2. WA1020101(プロジェクト登録画面)'!$E$71" display="'2. WA1020101(プロジェクト登録画面)'!$E$71" xr:uid="{8FA7F807-C8ED-4C8B-9A91-2BB776046753}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <sheetPr codeName="Sheet6">
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
-  <cols>
-    <col min="1" max="1" width="21" customWidth="1"/>
-    <col min="2" max="2" width="30.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.1640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A1" s="53" t="s">
-        <v>249</v>
-      </c>
-      <c r="B1" s="54" t="s">
-        <v>250</v>
-      </c>
-      <c r="C1" s="55" t="s">
-        <v>251</v>
-      </c>
-      <c r="D1" s="55" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A2" s="52" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="56" t="s">
-        <v>252</v>
-      </c>
-      <c r="C2" s="57" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="52" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A3" s="52" t="s">
-        <v>106</v>
-      </c>
-      <c r="B3" s="56" t="s">
-        <v>253</v>
-      </c>
-      <c r="C3" s="52" t="s">
-        <v>134</v>
-      </c>
-      <c r="D3" s="52" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A4" s="52" t="s">
-        <v>90</v>
-      </c>
-      <c r="B4" s="52" t="s">
-        <v>254</v>
-      </c>
-      <c r="C4" s="52" t="s">
-        <v>255</v>
-      </c>
-      <c r="D4" s="52" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A5" s="52" t="s">
-        <v>256</v>
-      </c>
-      <c r="B5" s="52" t="s">
-        <v>257</v>
-      </c>
-      <c r="C5" s="52" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A6" s="52" t="s">
-        <v>122</v>
-      </c>
-      <c r="C6" s="52" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A7" s="52" t="s">
-        <v>98</v>
-      </c>
-      <c r="C7" s="52" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A8" s="52" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A9" s="52" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A10" s="52" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A11" s="52" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A12" s="52" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A13" s="52" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A14" s="52" t="s">
-        <v>264</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="10"/>
-  <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9C264EB-0D84-4CFD-8555-A32FF9DB5129}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{463DB1CD-2869-4130-8F01-36FE749694ED}">
   <sheetPr codeName="SheetTemplate">
     <tabColor indexed="44"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U23"/>
+  <dimension ref="A1:AF27"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9.33203125" style="262"/>
-    <col min="2" max="11" width="17.6640625" style="262" customWidth="1"/>
-    <col min="12" max="19" width="4.5" style="262" customWidth="1"/>
-    <col min="20" max="20" width="98.1640625" style="262" customWidth="1"/>
-    <col min="21" max="26" width="4.5" style="262" customWidth="1"/>
+    <col min="2" max="14" width="17.6640625" style="262" customWidth="1"/>
+    <col min="15" max="26" width="4.5" style="262" customWidth="1"/>
     <col min="27" max="27" width="98.1640625" style="262" customWidth="1"/>
     <col min="28" max="16384" width="9.33203125" style="262"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.15">
       <c r="A1" s="261" t="s">
         <v>265</v>
       </c>
-      <c r="L1" s="263"/>
-      <c r="T1" s="264" t="s">
+      <c r="O1" s="263"/>
+      <c r="AA1" s="264" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.15">
       <c r="A2" s="262" t="s">
         <v>267</v>
       </c>
@@ -3639,9 +3455,9 @@
       <c r="G2" s="266"/>
       <c r="H2" s="266"/>
       <c r="I2" s="267"/>
-      <c r="L2" s="263"/>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="O2" s="263"/>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.15">
       <c r="A3" s="268" t="s">
         <v>269</v>
       </c>
@@ -3663,7 +3479,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.15">
       <c r="A4" s="271" t="s">
         <v>300</v>
       </c>
@@ -3687,12 +3503,12 @@
         <v>200</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.15">
       <c r="A6" s="261" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.15">
       <c r="B7" s="276" t="s">
         <v>277</v>
       </c>
@@ -3712,13 +3528,25 @@
         <v>282</v>
       </c>
       <c r="H7" s="270" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="I7" s="270" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" ht="27" x14ac:dyDescent="0.15">
+        <v>323</v>
+      </c>
+      <c r="J7" s="270" t="s">
+        <v>324</v>
+      </c>
+      <c r="K7" s="270" t="s">
+        <v>325</v>
+      </c>
+      <c r="L7" s="270" t="s">
+        <v>326</v>
+      </c>
+      <c r="M7" s="270" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" ht="27" x14ac:dyDescent="0.15">
       <c r="A8" s="269" t="s">
         <v>283</v>
       </c>
@@ -3741,18 +3569,26 @@
         <v>289</v>
       </c>
       <c r="H8" s="277" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="I8" s="277" t="s">
-        <v>335</v>
-      </c>
-      <c r="J8" s="279" t="s">
+        <v>329</v>
+      </c>
+      <c r="J8" s="277" t="s">
+        <v>330</v>
+      </c>
+      <c r="K8" s="277" t="s">
+        <v>331</v>
+      </c>
+      <c r="L8" s="277" t="s">
+        <v>332</v>
+      </c>
+      <c r="M8" s="277" t="s">
+        <v>333</v>
+      </c>
+      <c r="N8" s="279" t="s">
         <v>290</v>
       </c>
-      <c r="K8" s="280"/>
-      <c r="L8" s="280"/>
-      <c r="M8" s="280"/>
-      <c r="N8" s="280"/>
       <c r="O8" s="280"/>
       <c r="P8" s="280"/>
       <c r="Q8" s="280"/>
@@ -3760,51 +3596,74 @@
       <c r="S8" s="280"/>
       <c r="T8" s="280"/>
       <c r="U8" s="280"/>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="V8" s="280"/>
+      <c r="W8" s="280"/>
+      <c r="X8" s="280"/>
+      <c r="Y8" s="280"/>
+      <c r="Z8" s="280"/>
+      <c r="AA8" s="280"/>
+      <c r="AB8" s="280"/>
+      <c r="AC8" s="280"/>
+      <c r="AD8" s="280"/>
+      <c r="AE8" s="280"/>
+      <c r="AF8" s="280"/>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.15">
       <c r="A9" s="269" t="s">
         <v>291</v>
       </c>
       <c r="B9" s="281" t="str">
-        <f>IF(SUMIF($K15:$K23,$A9,L15:L23)=0,"",SUMIF($K15:$K23,$A9,L15:L23))</f>
+        <f>IF(SUMIF($K15:$K27,$A9,O15:O27)=0,"",SUMIF($K15:$K27,$A9,O15:O27))</f>
         <v/>
       </c>
       <c r="C9" s="281" t="str">
-        <f>IF(SUMIF($K15:$K23,$A9,M15:M23)=0,"",SUMIF($K15:$K23,$A9,M15:M23))</f>
+        <f>IF(SUMIF($K15:$K27,$A9,P15:P27)=0,"",SUMIF($K15:$K27,$A9,P15:P27))</f>
         <v/>
       </c>
       <c r="D9" s="281">
-        <f>IF(SUMIF($K15:$K23,$A9,N15:N23)=0,"",SUMIF($K15:$K23,$A9,N15:N23))</f>
+        <f>IF(SUMIF($K15:$K27,$A9,Q15:Q27)=0,"",SUMIF($K15:$K27,$A9,Q15:Q27))</f>
         <v>1</v>
       </c>
       <c r="E9" s="281" t="str">
-        <f>IF(SUMIF($K15:$K23,$A9,O15:O23)=0,"",SUMIF($K15:$K23,$A9,O15:O23))</f>
+        <f>IF(SUMIF($K15:$K27,$A9,R15:R27)=0,"",SUMIF($K15:$K27,$A9,R15:R27))</f>
         <v/>
       </c>
       <c r="F9" s="281" t="str">
-        <f>IF(SUMIF($K15:$K23,$A9,P15:P23)=0,"",SUMIF($K15:$K23,$A9,P15:P23))</f>
+        <f>IF(SUMIF($K15:$K27,$A9,S15:S27)=0,"",SUMIF($K15:$K27,$A9,S15:S27))</f>
         <v/>
       </c>
       <c r="G9" s="281" t="str">
-        <f>IF(SUMIF($K15:$K23,$A9,Q15:Q23)=0,"",SUMIF($K15:$K23,$A9,Q15:Q23))</f>
+        <f>IF(SUMIF($K15:$K27,$A9,T15:T27)=0,"",SUMIF($K15:$K27,$A9,T15:T27))</f>
         <v/>
       </c>
       <c r="H9" s="281" t="str">
-        <f>IF(SUMIF($K15:$K23,$A9,R15:R23)=0,"",SUMIF($K15:$K23,$A9,R15:R23))</f>
+        <f>IF(SUMIF($K15:$K27,$A9,U15:U27)=0,"",SUMIF($K15:$K27,$A9,U15:U27))</f>
         <v/>
       </c>
       <c r="I9" s="281" t="str">
-        <f>IF(SUMIF($K15:$K23,$A9,S15:S23)=0,"",SUMIF($K15:$K23,$A9,S15:S23))</f>
+        <f>IF(SUMIF($K15:$K27,$A9,V15:V27)=0,"",SUMIF($K15:$K27,$A9,V15:V27))</f>
         <v/>
       </c>
-      <c r="J9" s="282">
-        <f>SUM(B9:I9)</f>
+      <c r="J9" s="281" t="str">
+        <f>IF(SUMIF($K15:$K27,$A9,W15:W27)=0,"",SUMIF($K15:$K27,$A9,W15:W27))</f>
+        <v/>
+      </c>
+      <c r="K9" s="281" t="str">
+        <f>IF(SUMIF($K15:$K27,$A9,X15:X27)=0,"",SUMIF($K15:$K27,$A9,X15:X27))</f>
+        <v/>
+      </c>
+      <c r="L9" s="281" t="str">
+        <f>IF(SUMIF($K15:$K27,$A9,Y15:Y27)=0,"",SUMIF($K15:$K27,$A9,Y15:Y27))</f>
+        <v/>
+      </c>
+      <c r="M9" s="281" t="str">
+        <f>IF(SUMIF($K15:$K27,$A9,Z15:Z27)=0,"",SUMIF($K15:$K27,$A9,Z15:Z27))</f>
+        <v/>
+      </c>
+      <c r="N9" s="282">
+        <f>SUM(B9:M9)</f>
         <v>1</v>
       </c>
-      <c r="K9" s="261"/>
-      <c r="L9" s="261"/>
-      <c r="M9" s="261"/>
-      <c r="N9" s="261"/>
       <c r="O9" s="261"/>
       <c r="P9" s="261"/>
       <c r="Q9" s="261"/>
@@ -3812,51 +3671,74 @@
       <c r="S9" s="261"/>
       <c r="T9" s="261"/>
       <c r="U9" s="261"/>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="V9" s="261"/>
+      <c r="W9" s="261"/>
+      <c r="X9" s="261"/>
+      <c r="Y9" s="261"/>
+      <c r="Z9" s="261"/>
+      <c r="AA9" s="261"/>
+      <c r="AB9" s="261"/>
+      <c r="AC9" s="261"/>
+      <c r="AD9" s="261"/>
+      <c r="AE9" s="261"/>
+      <c r="AF9" s="261"/>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.15">
       <c r="A10" s="269" t="s">
         <v>292</v>
       </c>
       <c r="B10" s="281">
-        <f>IF(SUMIF($K15:$K23,$A10,L15:L23)=0,"",SUMIF($K15:$K23,$A10,L15:L23))</f>
+        <f>IF(SUMIF($K15:$K27,$A10,O15:O27)=0,"",SUMIF($K15:$K27,$A10,O15:O27))</f>
         <v>1</v>
       </c>
       <c r="C10" s="281">
-        <f>IF(SUMIF($K15:$K23,$A10,M15:M23)=0,"",SUMIF($K15:$K23,$A10,M15:M23))</f>
+        <f>IF(SUMIF($K15:$K27,$A10,P15:P27)=0,"",SUMIF($K15:$K27,$A10,P15:P27))</f>
         <v>1</v>
       </c>
       <c r="D10" s="281" t="str">
-        <f>IF(SUMIF($K15:$K23,$A10,N15:N23)=0,"",SUMIF($K15:$K23,$A10,N15:N23))</f>
+        <f>IF(SUMIF($K15:$K27,$A10,Q15:Q27)=0,"",SUMIF($K15:$K27,$A10,Q15:Q27))</f>
         <v/>
       </c>
       <c r="E10" s="281">
-        <f>IF(SUMIF($K15:$K23,$A10,O15:O23)=0,"",SUMIF($K15:$K23,$A10,O15:O23))</f>
+        <f>IF(SUMIF($K15:$K27,$A10,R15:R27)=0,"",SUMIF($K15:$K27,$A10,R15:R27))</f>
         <v>1</v>
       </c>
       <c r="F10" s="281">
-        <f>IF(SUMIF($K15:$K23,$A10,P15:P23)=0,"",SUMIF($K15:$K23,$A10,P15:P23))</f>
+        <f>IF(SUMIF($K15:$K27,$A10,S15:S27)=0,"",SUMIF($K15:$K27,$A10,S15:S27))</f>
         <v>1</v>
       </c>
       <c r="G10" s="281">
-        <f>IF(SUMIF($K15:$K23,$A10,Q15:Q23)=0,"",SUMIF($K15:$K23,$A10,Q15:Q23))</f>
+        <f>IF(SUMIF($K15:$K27,$A10,T15:T27)=0,"",SUMIF($K15:$K27,$A10,T15:T27))</f>
         <v>1</v>
       </c>
       <c r="H10" s="281">
-        <f>IF(SUMIF($K15:$K23,$A10,R15:R23)=0,"",SUMIF($K15:$K23,$A10,R15:R23))</f>
+        <f>IF(SUMIF($K15:$K27,$A10,U15:U27)=0,"",SUMIF($K15:$K27,$A10,U15:U27))</f>
         <v>1</v>
       </c>
       <c r="I10" s="281">
-        <f>IF(SUMIF($K15:$K23,$A10,S15:S23)=0,"",SUMIF($K15:$K23,$A10,S15:S23))</f>
+        <f>IF(SUMIF($K15:$K27,$A10,V15:V27)=0,"",SUMIF($K15:$K27,$A10,V15:V27))</f>
         <v>1</v>
       </c>
-      <c r="J10" s="282">
-        <f>SUM(B10:I10)</f>
-        <v>7</v>
-      </c>
-      <c r="K10" s="261"/>
-      <c r="L10" s="261"/>
-      <c r="M10" s="261"/>
-      <c r="N10" s="261"/>
+      <c r="J10" s="281">
+        <f>IF(SUMIF($K15:$K27,$A10,W15:W27)=0,"",SUMIF($K15:$K27,$A10,W15:W27))</f>
+        <v>1</v>
+      </c>
+      <c r="K10" s="281">
+        <f>IF(SUMIF($K15:$K27,$A10,X15:X27)=0,"",SUMIF($K15:$K27,$A10,X15:X27))</f>
+        <v>1</v>
+      </c>
+      <c r="L10" s="281">
+        <f>IF(SUMIF($K15:$K27,$A10,Y15:Y27)=0,"",SUMIF($K15:$K27,$A10,Y15:Y27))</f>
+        <v>1</v>
+      </c>
+      <c r="M10" s="281">
+        <f>IF(SUMIF($K15:$K27,$A10,Z15:Z27)=0,"",SUMIF($K15:$K27,$A10,Z15:Z27))</f>
+        <v>1</v>
+      </c>
+      <c r="N10" s="282">
+        <f>SUM(B10:M10)</f>
+        <v>11</v>
+      </c>
       <c r="O10" s="261"/>
       <c r="P10" s="261"/>
       <c r="Q10" s="261"/>
@@ -3864,8 +3746,19 @@
       <c r="S10" s="261"/>
       <c r="T10" s="261"/>
       <c r="U10" s="261"/>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="V10" s="261"/>
+      <c r="W10" s="261"/>
+      <c r="X10" s="261"/>
+      <c r="Y10" s="261"/>
+      <c r="Z10" s="261"/>
+      <c r="AA10" s="261"/>
+      <c r="AB10" s="261"/>
+      <c r="AC10" s="261"/>
+      <c r="AD10" s="261"/>
+      <c r="AE10" s="261"/>
+      <c r="AF10" s="261"/>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.15">
       <c r="A11" s="283" t="s">
         <v>290</v>
       </c>
@@ -3874,7 +3767,7 @@
         <v>1</v>
       </c>
       <c r="C11" s="284">
-        <f t="shared" ref="C11:I11" si="0">SUM(C9:C10)</f>
+        <f t="shared" ref="C11:M11" si="0">SUM(C9:C10)</f>
         <v>1</v>
       </c>
       <c r="D11" s="284">
@@ -3902,11 +3795,27 @@
         <v>1</v>
       </c>
       <c r="J11" s="284">
-        <f>SUM(B11:I11)</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.15">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="K11" s="284">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L11" s="284">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M11" s="284">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="N11" s="284">
+        <f>SUM(B11:M11)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.15">
       <c r="A12" s="261"/>
       <c r="B12" s="285"/>
       <c r="C12" s="285"/>
@@ -3918,8 +3827,11 @@
       <c r="I12" s="285"/>
       <c r="J12" s="285"/>
       <c r="K12" s="285"/>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="L12" s="285"/>
+      <c r="M12" s="285"/>
+      <c r="N12" s="285"/>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.15">
       <c r="A13" s="286" t="s">
         <v>293</v>
       </c>
@@ -3927,18 +3839,22 @@
       <c r="C13" s="287"/>
       <c r="D13" s="287"/>
       <c r="F13" s="287"/>
-      <c r="L13" s="263" t="s">
+      <c r="O13" s="263" t="s">
         <v>294</v>
       </c>
-      <c r="M13" s="263"/>
-      <c r="N13" s="263"/>
-      <c r="O13" s="263"/>
       <c r="P13" s="263"/>
       <c r="Q13" s="263"/>
       <c r="R13" s="263"/>
       <c r="S13" s="263"/>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="T13" s="263"/>
+      <c r="U13" s="263"/>
+      <c r="V13" s="263"/>
+      <c r="W13" s="263"/>
+      <c r="X13" s="263"/>
+      <c r="Y13" s="263"/>
+      <c r="Z13" s="263"/>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.15">
       <c r="A14" s="288" t="s">
         <v>295</v>
       </c>
@@ -3962,32 +3878,44 @@
       <c r="K14" s="293" t="s">
         <v>283</v>
       </c>
-      <c r="L14" s="294" t="s">
+      <c r="O14" s="294" t="s">
         <v>277</v>
       </c>
-      <c r="M14" s="294" t="s">
+      <c r="P14" s="294" t="s">
         <v>278</v>
       </c>
-      <c r="N14" s="294" t="s">
+      <c r="Q14" s="294" t="s">
         <v>279</v>
       </c>
-      <c r="O14" s="294" t="s">
+      <c r="R14" s="294" t="s">
         <v>280</v>
       </c>
-      <c r="P14" s="294" t="s">
+      <c r="S14" s="294" t="s">
         <v>281</v>
       </c>
-      <c r="Q14" s="294" t="s">
+      <c r="T14" s="294" t="s">
         <v>282</v>
       </c>
-      <c r="R14" s="294" t="s">
-        <v>332</v>
-      </c>
-      <c r="S14" s="294" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="U14" s="294" t="s">
+        <v>322</v>
+      </c>
+      <c r="V14" s="294" t="s">
+        <v>323</v>
+      </c>
+      <c r="W14" s="294" t="s">
+        <v>324</v>
+      </c>
+      <c r="X14" s="294" t="s">
+        <v>325</v>
+      </c>
+      <c r="Y14" s="294" t="s">
+        <v>326</v>
+      </c>
+      <c r="Z14" s="294" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A15" s="272" t="s">
         <v>38</v>
       </c>
@@ -4011,21 +3939,9 @@
       <c r="K15" s="272" t="s">
         <v>305</v>
       </c>
-      <c r="L15" s="295">
-        <f t="shared" ref="L15:S23" si="1">IF($D15=L$14,1,0)</f>
+      <c r="O15" s="295">
+        <f t="shared" ref="O15:Z27" si="1">IF($D15=O$14,1,0)</f>
         <v>1</v>
-      </c>
-      <c r="M15" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N15" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="O15" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
       </c>
       <c r="P15" s="295">
         <f t="shared" si="1"/>
@@ -4043,14 +3959,42 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T15" s="296" t="str">
+      <c r="T15" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U15" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W15" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X15" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y15" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z15" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA15" s="296" t="str">
         <f>IF(E15&lt;&gt;"",E15,"")</f>
         <v>レビュー指摘コメントの例。
 自動で挿入される名前とコロンの直後に指摘分類をa～iで書く。
 ※レビュー日時を書く場合はコロンの直後に*を書く。</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="40.5" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:32" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A16" s="272" t="s">
         <v>38</v>
       </c>
@@ -4074,25 +4018,13 @@
       <c r="K16" s="272" t="s">
         <v>305</v>
       </c>
-      <c r="L16" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M16" s="295">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="N16" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
       <c r="O16" s="295">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P16" s="295">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="295">
         <f t="shared" si="1"/>
@@ -4106,14 +4038,42 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T16" s="296" t="str">
+      <c r="T16" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U16" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z16" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA16" s="296" t="str">
         <f>IF(E16&lt;&gt;"",E16,"")</f>
         <v>対応内容の例。
 ---
 対応内容はデリミタ（---）の後に記入する。</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="67.5" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:27" ht="67.5" x14ac:dyDescent="0.15">
       <c r="A17" s="272" t="s">
         <v>38</v>
       </c>
@@ -4137,18 +4097,6 @@
       <c r="K17" s="272" t="s">
         <v>312</v>
       </c>
-      <c r="L17" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M17" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N17" s="295">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
       <c r="O17" s="295">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -4159,7 +4107,7 @@
       </c>
       <c r="Q17" s="295">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" s="295">
         <f t="shared" si="1"/>
@@ -4169,7 +4117,35 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T17" s="296" t="str">
+      <c r="T17" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U17" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W17" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X17" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y17" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z17" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA17" s="296" t="str">
         <f>IF(E17&lt;&gt;"",E17,"")</f>
         <v>対応内容を確認し、指摘をクローズする例。
 ---
@@ -4178,7 +4154,7 @@
 08/02山田 済</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A18" s="272" t="s">
         <v>38</v>
       </c>
@@ -4202,21 +4178,9 @@
       <c r="K18" s="272" t="s">
         <v>305</v>
       </c>
-      <c r="L18" s="295">
+      <c r="O18" s="295">
         <f t="shared" si="1"/>
         <v>0</v>
-      </c>
-      <c r="M18" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N18" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="O18" s="295">
-        <f t="shared" si="1"/>
-        <v>1</v>
       </c>
       <c r="P18" s="295">
         <f t="shared" si="1"/>
@@ -4228,18 +4192,46 @@
       </c>
       <c r="R18" s="295">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" s="295">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T18" s="296" t="str">
+      <c r="T18" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U18" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W18" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X18" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y18" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z18" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA18" s="296" t="str">
         <f>IF(E18&lt;&gt;"",E18,"")</f>
         <v>機能・仕様誤りの指摘例（カテゴリd）。</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A19" s="272" t="s">
         <v>38</v>
       </c>
@@ -4263,25 +4255,13 @@
       <c r="K19" s="272" t="s">
         <v>305</v>
       </c>
-      <c r="L19" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M19" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N19" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
       <c r="O19" s="295">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P19" s="295">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q19" s="295">
         <f t="shared" si="1"/>
@@ -4293,14 +4273,42 @@
       </c>
       <c r="S19" s="295">
         <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T19" s="295">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T19" s="296" t="str">
+      <c r="U19" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W19" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X19" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z19" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA19" s="296" t="str">
         <f>IF(E19&lt;&gt;"",E19,"")</f>
         <v>設計・ドキュメント規約違反の指摘例（カテゴリe）。</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A20" s="272" t="s">
         <v>38</v>
       </c>
@@ -4324,18 +4332,6 @@
       <c r="K20" s="272" t="s">
         <v>305</v>
       </c>
-      <c r="L20" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M20" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N20" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
       <c r="O20" s="295">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -4346,7 +4342,7 @@
       </c>
       <c r="Q20" s="295">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20" s="295">
         <f t="shared" si="1"/>
@@ -4356,26 +4352,54 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T20" s="296" t="str">
+      <c r="T20" s="295">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="U20" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W20" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X20" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y20" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z20" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA20" s="296" t="str">
         <f>IF(E20&lt;&gt;"",E20,"")</f>
         <v>記述誤りの指摘例（カテゴリf）。</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A21" s="272" t="s">
         <v>38</v>
       </c>
       <c r="B21" s="297" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C21" s="272" t="s">
         <v>302</v>
       </c>
       <c r="D21" s="272" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E21" s="271" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F21" s="271"/>
       <c r="G21" s="271"/>
@@ -4385,18 +4409,6 @@
       <c r="K21" s="272" t="s">
         <v>305</v>
       </c>
-      <c r="L21" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M21" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N21" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
       <c r="O21" s="295">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -4411,32 +4423,60 @@
       </c>
       <c r="R21" s="295">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" s="295">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T21" s="296" t="str">
+      <c r="T21" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U21" s="295">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="V21" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W21" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X21" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y21" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z21" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA21" s="296" t="str">
         <f>IF(E21&lt;&gt;"",E21,"")</f>
         <v>疑問点・確認の指摘例（カテゴリg）。</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A22" s="272" t="s">
         <v>38</v>
       </c>
       <c r="B22" s="297" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C22" s="272" t="s">
         <v>302</v>
       </c>
       <c r="D22" s="272" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E22" s="271" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="F22" s="271"/>
       <c r="G22" s="271"/>
@@ -4446,18 +4486,6 @@
       <c r="K22" s="272" t="s">
         <v>305</v>
       </c>
-      <c r="L22" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M22" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N22" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
       <c r="O22" s="295">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -4476,36 +4504,64 @@
       </c>
       <c r="S22" s="295">
         <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T22" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U22" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="295">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="T22" s="296" t="str">
+      <c r="W22" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X22" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y22" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z22" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA22" s="296" t="str">
         <f>IF(E22&lt;&gt;"",E22,"")</f>
         <v>改善要望の指摘例（カテゴリh）。</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.15">
-      <c r="A23" s="272"/>
-      <c r="B23" s="272"/>
-      <c r="C23" s="272"/>
-      <c r="D23" s="272"/>
-      <c r="E23" s="271"/>
+    <row r="23" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="A23" s="272" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="297" t="s">
+        <v>340</v>
+      </c>
+      <c r="C23" s="272" t="s">
+        <v>302</v>
+      </c>
+      <c r="D23" s="272" t="s">
+        <v>341</v>
+      </c>
+      <c r="E23" s="271" t="s">
+        <v>342</v>
+      </c>
       <c r="F23" s="271"/>
       <c r="G23" s="271"/>
       <c r="H23" s="271"/>
       <c r="I23" s="271"/>
       <c r="J23" s="271"/>
-      <c r="K23" s="272"/>
-      <c r="L23" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M23" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N23" s="295">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="K23" s="272" t="s">
+        <v>305</v>
       </c>
       <c r="O23" s="295">
         <f t="shared" si="1"/>
@@ -4527,15 +4583,343 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T23" s="296" t="str">
+      <c r="T23" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U23" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="295">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="X23" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y23" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z23" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA23" s="296" t="str">
         <f>IF(E23&lt;&gt;"",E23,"")</f>
+        <v>仕様変更の指摘例（カテゴリi）。</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="A24" s="272" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="297" t="s">
+        <v>343</v>
+      </c>
+      <c r="C24" s="272" t="s">
+        <v>302</v>
+      </c>
+      <c r="D24" s="272" t="s">
+        <v>344</v>
+      </c>
+      <c r="E24" s="271" t="s">
+        <v>345</v>
+      </c>
+      <c r="F24" s="271"/>
+      <c r="G24" s="271"/>
+      <c r="H24" s="271"/>
+      <c r="I24" s="271"/>
+      <c r="J24" s="271"/>
+      <c r="K24" s="272" t="s">
+        <v>305</v>
+      </c>
+      <c r="O24" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P24" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q24" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="R24" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S24" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T24" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U24" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W24" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X24" s="295">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Y24" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z24" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA24" s="296" t="str">
+        <f>IF(E24&lt;&gt;"",E24,"")</f>
+        <v>テスト項目漏れの指摘例（カテゴリj）。</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="A25" s="272" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="297" t="s">
+        <v>346</v>
+      </c>
+      <c r="C25" s="272" t="s">
+        <v>302</v>
+      </c>
+      <c r="D25" s="272" t="s">
+        <v>347</v>
+      </c>
+      <c r="E25" s="271" t="s">
+        <v>348</v>
+      </c>
+      <c r="F25" s="271"/>
+      <c r="G25" s="271"/>
+      <c r="H25" s="271"/>
+      <c r="I25" s="271"/>
+      <c r="J25" s="271"/>
+      <c r="K25" s="272" t="s">
+        <v>305</v>
+      </c>
+      <c r="O25" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P25" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q25" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="R25" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S25" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T25" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U25" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W25" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X25" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="295">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Z25" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA25" s="296" t="str">
+        <f>IF(E25&lt;&gt;"",E25,"")</f>
+        <v>テスト漏れの指摘例（カテゴリk）。</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="A26" s="272" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="297" t="s">
+        <v>349</v>
+      </c>
+      <c r="C26" s="272" t="s">
+        <v>302</v>
+      </c>
+      <c r="D26" s="272" t="s">
+        <v>350</v>
+      </c>
+      <c r="E26" s="271" t="s">
+        <v>351</v>
+      </c>
+      <c r="F26" s="271"/>
+      <c r="G26" s="271"/>
+      <c r="H26" s="271"/>
+      <c r="I26" s="271"/>
+      <c r="J26" s="271"/>
+      <c r="K26" s="272" t="s">
+        <v>305</v>
+      </c>
+      <c r="O26" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P26" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q26" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="R26" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S26" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T26" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X26" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y26" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z26" s="295">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="AA26" s="296" t="str">
+        <f>IF(E26&lt;&gt;"",E26,"")</f>
+        <v>その他の指摘例（カテゴリl）。</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="A27" s="272"/>
+      <c r="B27" s="272"/>
+      <c r="C27" s="272"/>
+      <c r="D27" s="272"/>
+      <c r="E27" s="271"/>
+      <c r="F27" s="271"/>
+      <c r="G27" s="271"/>
+      <c r="H27" s="271"/>
+      <c r="I27" s="271"/>
+      <c r="J27" s="271"/>
+      <c r="K27" s="272"/>
+      <c r="O27" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P27" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q27" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="R27" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S27" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T27" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X27" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Y27" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z27" s="295">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA27" s="296" t="str">
+        <f>IF(E27&lt;&gt;"",E27,"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="15">
     <mergeCell ref="E22:J22"/>
     <mergeCell ref="E23:J23"/>
+    <mergeCell ref="E24:J24"/>
+    <mergeCell ref="E25:J25"/>
+    <mergeCell ref="E26:J26"/>
+    <mergeCell ref="E27:J27"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="E15:J15"/>
@@ -4547,33 +4931,37 @@
     <mergeCell ref="E21:J21"/>
   </mergeCells>
   <phoneticPr fontId="10"/>
-  <conditionalFormatting sqref="A15:K23">
+  <conditionalFormatting sqref="A15:K27">
     <cfRule type="expression" dxfId="0" priority="1" stopIfTrue="1">
       <formula>$K15="済"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K15:K23" xr:uid="{DADE2831-03EF-4F2D-9003-C369729E8317}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K15:N27" xr:uid="{FBE1A021-E2DD-489F-ABF7-2815DC370902}">
       <formula1>"未,済"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="B15" location="'2. WA1020101(プロジェクト登録画面)'!$B$5" display="'2. WA1020101(プロジェクト登録画面)'!$B$5" xr:uid="{8571D6C5-1299-4C7C-B9AF-671C75EE0CC2}"/>
-    <hyperlink ref="B16" location="'2. WA1020101(プロジェクト登録画面)'!$E$60" display="'2. WA1020101(プロジェクト登録画面)'!$E$60" xr:uid="{FBBDEE91-024C-4BE1-A8F8-8CBB7F22E126}"/>
-    <hyperlink ref="B17" location="'2. WA1020101(プロジェクト登録画面)'!$E$62" display="'2. WA1020101(プロジェクト登録画面)'!$E$62" xr:uid="{DAEE31CA-8FB6-4CC5-A807-D43D65237713}"/>
-    <hyperlink ref="B18" location="'2. WA1020101(プロジェクト登録画面)'!$E$63" display="'2. WA1020101(プロジェクト登録画面)'!$E$63" xr:uid="{9E125C1B-F9F2-4361-BD92-DBDC4EDC0342}"/>
-    <hyperlink ref="B19" location="'2. WA1020101(プロジェクト登録画面)'!$E$64" display="'2. WA1020101(プロジェクト登録画面)'!$E$64" xr:uid="{20E27398-459B-4753-80A9-9803454E57C3}"/>
-    <hyperlink ref="B20" location="'2. WA1020101(プロジェクト登録画面)'!$E$65" display="'2. WA1020101(プロジェクト登録画面)'!$E$65" xr:uid="{120A5A9F-929D-4219-B72D-808D3E90040E}"/>
-    <hyperlink ref="B21" location="'2. WA1020101(プロジェクト登録画面)'!$E$66" display="'2. WA1020101(プロジェクト登録画面)'!$E$66" xr:uid="{C9BB56BC-279A-4A99-8F42-28D332D7C62C}"/>
-    <hyperlink ref="B22" location="'2. WA1020101(プロジェクト登録画面)'!$E$67" display="'2. WA1020101(プロジェクト登録画面)'!$E$67" xr:uid="{1C1D0796-5A4C-425D-8863-6DDD93E1B09F}"/>
+    <hyperlink ref="B15" location="'2. WA1020101(プロジェクト登録画面)'!$B$5" display="'2. WA1020101(プロジェクト登録画面)'!$B$5" xr:uid="{34E56944-1A33-443B-8D1B-EB2187C0D81B}"/>
+    <hyperlink ref="B16" location="'2. WA1020101(プロジェクト登録画面)'!$E$60" display="'2. WA1020101(プロジェクト登録画面)'!$E$60" xr:uid="{71F99892-F3A4-4AC2-BBEA-F8ECEE31EBBA}"/>
+    <hyperlink ref="B17" location="'2. WA1020101(プロジェクト登録画面)'!$E$62" display="'2. WA1020101(プロジェクト登録画面)'!$E$62" xr:uid="{CFECC20D-87CB-4A93-BEFB-07EA6313EA6E}"/>
+    <hyperlink ref="B18" location="'2. WA1020101(プロジェクト登録画面)'!$E$63" display="'2. WA1020101(プロジェクト登録画面)'!$E$63" xr:uid="{85516C35-EF9A-46A9-8358-6E677107438E}"/>
+    <hyperlink ref="B19" location="'2. WA1020101(プロジェクト登録画面)'!$E$64" display="'2. WA1020101(プロジェクト登録画面)'!$E$64" xr:uid="{45329672-902F-4BAA-A8D4-8627D8FAF2E9}"/>
+    <hyperlink ref="B20" location="'2. WA1020101(プロジェクト登録画面)'!$E$65" display="'2. WA1020101(プロジェクト登録画面)'!$E$65" xr:uid="{C365A3CE-574E-47B1-B356-6BB9A4B5AEFA}"/>
+    <hyperlink ref="B21" location="'2. WA1020101(プロジェクト登録画面)'!$E$66" display="'2. WA1020101(プロジェクト登録画面)'!$E$66" xr:uid="{28815E1C-709B-4B7A-AF1E-3A07E6A6B952}"/>
+    <hyperlink ref="B22" location="'2. WA1020101(プロジェクト登録画面)'!$E$67" display="'2. WA1020101(プロジェクト登録画面)'!$E$67" xr:uid="{CF26257E-DC35-40CD-925F-81B152CE4B7B}"/>
+    <hyperlink ref="B23" location="'2. WA1020101(プロジェクト登録画面)'!$E$68" display="'2. WA1020101(プロジェクト登録画面)'!$E$68" xr:uid="{A1264CB9-AD6E-40CC-9ADB-DCC817F9ABCE}"/>
+    <hyperlink ref="B24" location="'2. WA1020101(プロジェクト登録画面)'!$E$69" display="'2. WA1020101(プロジェクト登録画面)'!$E$69" xr:uid="{003E4CA7-70CE-4C27-AA9B-AE0335BED7F0}"/>
+    <hyperlink ref="B25" location="'2. WA1020101(プロジェクト登録画面)'!$E$70" display="'2. WA1020101(プロジェクト登録画面)'!$E$70" xr:uid="{803EF682-F254-416A-A957-F94CFBE85B36}"/>
+    <hyperlink ref="B26" location="'2. WA1020101(プロジェクト登録画面)'!$E$71" display="'2. WA1020101(プロジェクト登録画面)'!$E$71" xr:uid="{FDB7DF19-73CF-4CD2-9507-2FE14DE250C6}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
-  <pageSetup paperSize="9" scale="86" orientation="landscape" verticalDpi="200" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="67" orientation="landscape" verticalDpi="200" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet3">
     <pageSetUpPr fitToPage="1"/>
@@ -5253,7 +5641,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2">
     <pageSetUpPr fitToPage="1"/>
@@ -6814,7 +7202,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet4">
     <pageSetUpPr fitToPage="1"/>
@@ -7560,7 +7948,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet5">
     <pageSetUpPr fitToPage="1"/>
@@ -8066,7 +8454,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet7">
     <pageSetUpPr fitToPage="1"/>
@@ -12367,7 +12755,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet8">
     <pageSetUpPr fitToPage="1"/>
@@ -15886,7 +16274,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
@@ -17056,4 +17444,143 @@
     <brk id="33" max="34" man="1"/>
   </rowBreaks>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <sheetPr codeName="Sheet6">
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="21" customWidth="1"/>
+    <col min="2" max="2" width="30.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A1" s="53" t="s">
+        <v>249</v>
+      </c>
+      <c r="B1" s="54" t="s">
+        <v>250</v>
+      </c>
+      <c r="C1" s="55" t="s">
+        <v>251</v>
+      </c>
+      <c r="D1" s="55" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A2" s="52" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="56" t="s">
+        <v>252</v>
+      </c>
+      <c r="C2" s="57" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="52" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A3" s="52" t="s">
+        <v>106</v>
+      </c>
+      <c r="B3" s="56" t="s">
+        <v>253</v>
+      </c>
+      <c r="C3" s="52" t="s">
+        <v>134</v>
+      </c>
+      <c r="D3" s="52" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A4" s="52" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" s="52" t="s">
+        <v>254</v>
+      </c>
+      <c r="C4" s="52" t="s">
+        <v>255</v>
+      </c>
+      <c r="D4" s="52" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A5" s="52" t="s">
+        <v>256</v>
+      </c>
+      <c r="B5" s="52" t="s">
+        <v>257</v>
+      </c>
+      <c r="C5" s="52" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A6" s="52" t="s">
+        <v>122</v>
+      </c>
+      <c r="C6" s="52" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A7" s="52" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="52" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A8" s="52" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A9" s="52" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A10" s="52" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A11" s="52" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A12" s="52" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A13" s="52" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A14" s="52" t="s">
+        <v>264</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="10"/>
+  <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+</worksheet>
 </file>
--- a/doctool/test/auto/scenario27/システム機能設計書_サンプル_S27_expected.xlsx
+++ b/doctool/test/auto/scenario27/システム機能設計書_サンプル_S27_expected.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PJ\01.Nablarch\repo\review-support-tool\doctool\test\temp_dir\scenario26\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PJ\01.Nablarch\repo\review-support-tool\doctool\test\temp_dir\scenario27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4663F348-E824-49E9-B1E2-2B511BA4949C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2F6850B-088C-454C-A31E-73339299A9D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="38700" windowHeight="15345" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="レビュー結果1回目" sheetId="11" r:id="rId1"/>
@@ -1329,7 +1329,7 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>システム機能設計書_サンプル_S26</t>
+    <t>システム機能設計書_サンプル_S27</t>
   </si>
   <si>
     <t>B5</t>
@@ -3420,7 +3420,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{463DB1CD-2869-4130-8F01-36FE749694ED}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28068030-4B40-4E63-8BEA-20DD6C22DF04}">
   <sheetPr codeName="SheetTemplate">
     <tabColor indexed="44"/>
     <pageSetUpPr fitToPage="1"/>
@@ -4937,23 +4937,23 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K15:N27" xr:uid="{FBE1A021-E2DD-489F-ABF7-2815DC370902}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K15:N27" xr:uid="{46360D96-D2FA-4FD3-8BCA-FF702B514782}">
       <formula1>"未,済"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="B15" location="'2. WA1020101(プロジェクト登録画面)'!$B$5" display="'2. WA1020101(プロジェクト登録画面)'!$B$5" xr:uid="{34E56944-1A33-443B-8D1B-EB2187C0D81B}"/>
-    <hyperlink ref="B16" location="'2. WA1020101(プロジェクト登録画面)'!$E$60" display="'2. WA1020101(プロジェクト登録画面)'!$E$60" xr:uid="{71F99892-F3A4-4AC2-BBEA-F8ECEE31EBBA}"/>
-    <hyperlink ref="B17" location="'2. WA1020101(プロジェクト登録画面)'!$E$62" display="'2. WA1020101(プロジェクト登録画面)'!$E$62" xr:uid="{CFECC20D-87CB-4A93-BEFB-07EA6313EA6E}"/>
-    <hyperlink ref="B18" location="'2. WA1020101(プロジェクト登録画面)'!$E$63" display="'2. WA1020101(プロジェクト登録画面)'!$E$63" xr:uid="{85516C35-EF9A-46A9-8358-6E677107438E}"/>
-    <hyperlink ref="B19" location="'2. WA1020101(プロジェクト登録画面)'!$E$64" display="'2. WA1020101(プロジェクト登録画面)'!$E$64" xr:uid="{45329672-902F-4BAA-A8D4-8627D8FAF2E9}"/>
-    <hyperlink ref="B20" location="'2. WA1020101(プロジェクト登録画面)'!$E$65" display="'2. WA1020101(プロジェクト登録画面)'!$E$65" xr:uid="{C365A3CE-574E-47B1-B356-6BB9A4B5AEFA}"/>
-    <hyperlink ref="B21" location="'2. WA1020101(プロジェクト登録画面)'!$E$66" display="'2. WA1020101(プロジェクト登録画面)'!$E$66" xr:uid="{28815E1C-709B-4B7A-AF1E-3A07E6A6B952}"/>
-    <hyperlink ref="B22" location="'2. WA1020101(プロジェクト登録画面)'!$E$67" display="'2. WA1020101(プロジェクト登録画面)'!$E$67" xr:uid="{CF26257E-DC35-40CD-925F-81B152CE4B7B}"/>
-    <hyperlink ref="B23" location="'2. WA1020101(プロジェクト登録画面)'!$E$68" display="'2. WA1020101(プロジェクト登録画面)'!$E$68" xr:uid="{A1264CB9-AD6E-40CC-9ADB-DCC817F9ABCE}"/>
-    <hyperlink ref="B24" location="'2. WA1020101(プロジェクト登録画面)'!$E$69" display="'2. WA1020101(プロジェクト登録画面)'!$E$69" xr:uid="{003E4CA7-70CE-4C27-AA9B-AE0335BED7F0}"/>
-    <hyperlink ref="B25" location="'2. WA1020101(プロジェクト登録画面)'!$E$70" display="'2. WA1020101(プロジェクト登録画面)'!$E$70" xr:uid="{803EF682-F254-416A-A957-F94CFBE85B36}"/>
-    <hyperlink ref="B26" location="'2. WA1020101(プロジェクト登録画面)'!$E$71" display="'2. WA1020101(プロジェクト登録画面)'!$E$71" xr:uid="{FDB7DF19-73CF-4CD2-9507-2FE14DE250C6}"/>
+    <hyperlink ref="B15" location="'2. WA1020101(プロジェクト登録画面)'!$B$5" display="'2. WA1020101(プロジェクト登録画面)'!$B$5" xr:uid="{C6EE804D-2998-4365-AE71-370ED30E7F45}"/>
+    <hyperlink ref="B16" location="'2. WA1020101(プロジェクト登録画面)'!$E$60" display="'2. WA1020101(プロジェクト登録画面)'!$E$60" xr:uid="{992915C9-4925-4BC8-8229-4BDE1CEECFDB}"/>
+    <hyperlink ref="B17" location="'2. WA1020101(プロジェクト登録画面)'!$E$62" display="'2. WA1020101(プロジェクト登録画面)'!$E$62" xr:uid="{495ED133-AAC8-4663-87DE-4FA3234C6FA2}"/>
+    <hyperlink ref="B18" location="'2. WA1020101(プロジェクト登録画面)'!$E$63" display="'2. WA1020101(プロジェクト登録画面)'!$E$63" xr:uid="{A6D3B8EB-99AC-4FF4-AB0F-21D1DF9DB253}"/>
+    <hyperlink ref="B19" location="'2. WA1020101(プロジェクト登録画面)'!$E$64" display="'2. WA1020101(プロジェクト登録画面)'!$E$64" xr:uid="{CEE2715D-8C73-4CB3-9855-12BF92E67EE8}"/>
+    <hyperlink ref="B20" location="'2. WA1020101(プロジェクト登録画面)'!$E$65" display="'2. WA1020101(プロジェクト登録画面)'!$E$65" xr:uid="{14D95EB1-0343-4354-9C3B-088DA644FF36}"/>
+    <hyperlink ref="B21" location="'2. WA1020101(プロジェクト登録画面)'!$E$66" display="'2. WA1020101(プロジェクト登録画面)'!$E$66" xr:uid="{881F78E5-918F-4270-A975-DBE868E55579}"/>
+    <hyperlink ref="B22" location="'2. WA1020101(プロジェクト登録画面)'!$E$67" display="'2. WA1020101(プロジェクト登録画面)'!$E$67" xr:uid="{3538E812-2170-4E16-9D03-9851862B6A5A}"/>
+    <hyperlink ref="B23" location="'2. WA1020101(プロジェクト登録画面)'!$E$68" display="'2. WA1020101(プロジェクト登録画面)'!$E$68" xr:uid="{EB5F2049-C2DD-4D3F-A4A2-642C7EF4BB0E}"/>
+    <hyperlink ref="B24" location="'2. WA1020101(プロジェクト登録画面)'!$E$69" display="'2. WA1020101(プロジェクト登録画面)'!$E$69" xr:uid="{8729841B-12FA-45C5-BF71-6ADD84035488}"/>
+    <hyperlink ref="B25" location="'2. WA1020101(プロジェクト登録画面)'!$E$70" display="'2. WA1020101(プロジェクト登録画面)'!$E$70" xr:uid="{3AC71914-C365-4A1A-B400-C31E89283800}"/>
+    <hyperlink ref="B26" location="'2. WA1020101(プロジェクト登録画面)'!$E$71" display="'2. WA1020101(プロジェクト登録画面)'!$E$71" xr:uid="{2C1E3C32-9540-4033-A5AA-D887D8294C12}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
   <pageSetup paperSize="9" scale="67" orientation="landscape" verticalDpi="200" r:id="rId1"/>
